--- a/실습파일/실습4_절약모드_배치API.xlsx
+++ b/실습파일/실습4_절약모드_배치API.xlsx
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="C1:C48"/>
+  <dimension ref="C2:C48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="3" customWidth="1" style="26" min="1" max="1"/>
@@ -642,7 +642,6 @@
     <col width="104" customWidth="1" style="26" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="30" customHeight="1" s="26">
       <c r="C2" s="1" t="inlineStr">
         <is>
@@ -681,11 +680,10 @@
     <row r="7">
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>학생부 220명, 서술형 300장처럼 오늘 밤에 걸어 두고 내일 아침에 받으면 되는 일에 딱 맞습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
+          <t>학생부 220명, 서술형 300장처럼 지금 당장 눈앞에 있어야 하는 것은 아닌 일에 씁니다. 실제로 돌려 보면 몇 분 만에 끝나 있는 경우가 많습니다. 다만 몇 시에 끝난다는 약속은 아닙니다.</t>
+        </is>
+      </c>
+    </row>
     <row r="9" ht="24" customHeight="1" s="26">
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -707,7 +705,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13" ht="24" customHeight="1" s="26">
       <c r="C13" s="3" t="inlineStr">
         <is>
@@ -778,11 +775,10 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24" ht="24" customHeight="1" s="26">
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>결과 받기   (몇 시간 뒤)</t>
+          <t>결과 받기   (대개 몇 분 뒤 · 제출하고 24시간 안에)</t>
         </is>
       </c>
     </row>
@@ -814,7 +810,6 @@
         </is>
       </c>
     </row>
-    <row r="29"/>
     <row r="30" ht="24" customHeight="1" s="26">
       <c r="C30" s="3" t="inlineStr">
         <is>
@@ -850,7 +845,6 @@
         </is>
       </c>
     </row>
-    <row r="35"/>
     <row r="36" ht="24" customHeight="1" s="26">
       <c r="C36" s="3" t="inlineStr">
         <is>
@@ -879,7 +873,6 @@
         </is>
       </c>
     </row>
-    <row r="40"/>
     <row r="41" ht="32" customHeight="1" s="26">
       <c r="C41" s="5" t="inlineStr">
         <is>
@@ -894,7 +887,6 @@
         </is>
       </c>
     </row>
-    <row r="43"/>
     <row r="44" ht="24" customHeight="1" s="26">
       <c r="C44" s="3" t="inlineStr">
         <is>
@@ -926,7 +918,7 @@
     <row r="48" ht="32" customHeight="1" s="26">
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>답 →  ① 됩니다. 컴퓨터를 꺼도 됩니다.   ② C:\MyTrustedFiles\BatchResults 폴더에 새로 만들어지는 엑셀 파일.   ③ 안 됩니다. 보통 수 시간이지만 최대 24시간(GPT) / 48시간(Gemini) 이 걸릴 수 있어 급한 일은 미션 1의 실시간 방식을 쓰세요.</t>
+          <t>답 →  ① 됩니다. 컴퓨터를 꺼도 됩니다.   ② C:\MyTrustedFiles\BatchResults 폴더에 새로 만들어지는 엑셀 파일.   ③ 안 됩니다. 대개 몇 분이면 끝나지만 몇 시에 끝난다는 약속이 아니라서, 시각을 다투는 일은 미션 1의 실시간 방식을 쓰세요.</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1746,7 @@
     <row r="20">
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>절약 모드는 표준 단가의 정확히 50% 입니다. 대신 결과가 몇 시간 뒤에 나옵니다.</t>
+          <t>절약 모드는 표준 단가의 정확히 50% 입니다. 대신 언제 끝난다는 약속이 없습니다 — 대개 몇 분이면 나오지만 길면 수 시간입니다. 제출하고 24시간 안에 한 번 확인하세요.</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1839,8 @@
       </c>
       <c r="D6" s="23" t="inlineStr">
         <is>
-          <t>보통 수 시간, 최대 24시간(GPT) / 48시간(Gemini)</t>
+          <t>대개 몇 분, 길면 수 시간 — 약속된 시각이 없음
+(한도는 제출 시각부터 : GPT 24시간 / Gemini 48시간)</t>
         </is>
       </c>
     </row>
@@ -1968,7 +1961,7 @@
       <c r="D13" s="23" t="inlineStr">
         <is>
           <t>100행 넘는 대량 작업
-밤에 걸어 두고 아침에 받을 때</t>
+시각을 다투지 않는 일</t>
         </is>
       </c>
     </row>

--- a/실습파일/실습4_절약모드_배치API.xlsx
+++ b/실습파일/실습4_절약모드_배치API.xlsx
@@ -652,7 +652,7 @@
     <row r="3">
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>걸리는 시간: 약 7분   (심화 코스)   |   [데이터] 탭 → [API 메뉴] → [DRM AI v10.0] → [GPT 실행] 또는 [Gemini 실행]</t>
+          <t>걸리는 시간: 약 7분   (심화 코스)   |   [데이터] 탭 → [API 메뉴] → [DRM AI v10.7] → [GPT 실행] 또는 [Gemini 실행]</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
     <row r="7">
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>학생부 220명, 서술형 300장처럼 지금 당장 눈앞에 있어야 하는 것은 아닌 일에 씁니다. 실제로 돌려 보면 몇 분 만에 끝나 있는 경우가 많습니다. 다만 몇 시에 끝난다는 약속은 아닙니다.</t>
+          <t>학생부 220명, 서술형 300장처럼 지금 당장 눈앞에 있어야 하는 것은 아닌 일에 씁니다. 보통 수 시간 걸리고, 최대 GPT 24시간 · Gemini 48시간입니다. 빨리 끝날 때도 있지만 시간을 약속하지는 않습니다.</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
     <row r="15" ht="34" customHeight="1" s="26">
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>2.  [데이터] 탭 → [API 메뉴] → [DRM AI v10.0] → [Gemini 실행] → [Gemini로 글과 파일, 이미지 행 단위 처리 - 절약 모드(Batch API, 50% 할인)]</t>
+          <t>2.  [데이터] 탭 → [API 메뉴] → [DRM AI v10.7] → [Gemini 실행] → [Gemini로 글과 파일, 이미지 행 단위 처리 - 절약 모드(Batch API, 50% 할인)]</t>
         </is>
       </c>
     </row>
@@ -778,14 +778,14 @@
     <row r="24" ht="24" customHeight="1" s="26">
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>결과 받기   (대개 몇 분 뒤 · 제출하고 24시간 안에)</t>
+          <t>결과 받기   (보통 수 시간 뒤 · 제출하고 GPT 24시간 / Gemini 48시간 안에)</t>
         </is>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1" s="26">
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>1.  [데이터] 탭 → [API 메뉴] → [DRM AI v10.0] → [Gemini 실행] → [배치 처리 상태 확인 / 결과 받기]</t>
+          <t>1.  [데이터] 탭 → [API 메뉴] → [DRM AI v10.7] → [Gemini 실행] → [배치 처리 상태 확인 / 결과 받기]</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
     <row r="48" ht="32" customHeight="1" s="26">
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>답 →  ① 됩니다. 컴퓨터를 꺼도 됩니다.   ② C:\MyTrustedFiles\BatchResults 폴더에 새로 만들어지는 엑셀 파일.   ③ 안 됩니다. 대개 몇 분이면 끝나지만 몇 시에 끝난다는 약속이 아니라서, 시각을 다투는 일은 미션 1의 실시간 방식을 쓰세요.</t>
+          <t>답 →  ① 됩니다. 컴퓨터를 꺼도 됩니다.   ② C:\MyTrustedFiles\BatchResults 폴더에 새로 만들어지는 엑셀 파일.   ③ 안 됩니다. 보통 수 시간 걸리고 몇 시에 끝난다는 약속이 없어서, 시각을 다투는 일은 미션 1의 실시간 방식을 쓰세요.</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G23"/>
+  <dimension ref="B2:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="3" customWidth="1" style="26" min="1" max="1"/>
@@ -1621,7 +1621,7 @@
     <row r="13">
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>gemini-3.7-flash  (권장·가장 쌈)</t>
+          <t>gemini-3.7-flash  (권장)</t>
         </is>
       </c>
       <c r="C13" s="17" t="n">
@@ -1646,14 +1646,14 @@
     <row r="14">
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>gpt-5.6-luna</t>
+          <t>gpt-6-luna</t>
         </is>
       </c>
       <c r="C14" s="17" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D14" s="17" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="E14" s="28">
         <f>ROUND(($C$6*$C$7/1000000*C14 + $C$6*$C$8/1000000*D14)*$C$9,0)</f>
@@ -1671,14 +1671,14 @@
     <row r="15">
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>gpt-5.6-terra</t>
+          <t>gpt-6-sol</t>
         </is>
       </c>
       <c r="C15" s="17" t="n">
         <v>2</v>
       </c>
       <c r="D15" s="17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E15" s="28">
         <f>ROUND(($C$6*$C$7/1000000*C15 + $C$6*$C$8/1000000*D15)*$C$9,0)</f>
@@ -1696,14 +1696,14 @@
     <row r="16">
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>gpt-5.6-sol  (가장 똑똑·가장 비쌈)</t>
+          <t>gpt-6.1-sol  (GPT 최신)</t>
         </is>
       </c>
       <c r="C16" s="17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D16" s="17" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E16" s="28">
         <f>ROUND(($C$6*$C$7/1000000*C16 + $C$6*$C$8/1000000*D16)*$C$9,0)</f>
@@ -1746,21 +1746,35 @@
     <row r="20">
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>절약 모드는 표준 단가의 정확히 50% 입니다. 대신 언제 끝난다는 약속이 없습니다 — 대개 몇 분이면 나오지만 길면 수 시간입니다. 제출하고 24시간 안에 한 번 확인하세요.</t>
+          <t>절약 모드는 표준 단가의 정확히 50% 입니다. 대신 언제 끝난다는 약속이 없습니다 — 보통 수 시간 걸리고, 최대 GPT 24시간 · Gemini 48시간입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>빨리 끝날 때도 있지만 시간을 약속하지는 않습니다. 제출하고 GPT 는 24시간, Gemini 는 48시간 안에 한 번 확인하세요.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="21" t="inlineStr">
         <is>
-          <t>단가 기준: 2026-08 확인.  gemini-3.7-flash 는 2026-12-31 까지 이벤트 단가($0.75/$3.75)이고 2027-01-01 부터 정가($1.50/$7.50)로 바뀝니다.</t>
+          <t>단가 기준: 2026-10 확인.  gemini-3.7-flash 는 2026-12-31 까지 이벤트 단가($0.75/$3.75)이고 2027-01-01 부터 정가($1.50/$7.50)로 바뀝니다.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="21" t="inlineStr">
         <is>
-          <t>실제 청구액은 [안내 및 설정] → [사용 내역 내보내기] 에서 확인하세요. 이 표는 감을 잡기 위한 어림값입니다.</t>
+          <t>참고용 달러 값(실제 청구액과 다를 수 있습니다 — 실제 청구는 OpenAI·Google 결제 화면)은 [안내 및 설정] → [사용 내역 내보내기] 에서 확인하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>이 표는 감을 잡기 위한 어림값입니다.</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1853,7 @@
       </c>
       <c r="D6" s="23" t="inlineStr">
         <is>
-          <t>대개 몇 분, 길면 수 시간 — 약속된 시각이 없음
+          <t>보통 수 시간 — 약속된 시각이 없음
 (한도는 제출 시각부터 : GPT 24시간 / Gemini 48시간)</t>
         </is>
       </c>
